--- a/output/pdf_financials_xlsx/STW.xlsx
+++ b/output/pdf_financials_xlsx/STW.xlsx
@@ -1135,31 +1135,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.000943</v>
+        <v>-0.000943</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.06753000000000001</v>
+        <v>-0.06753000000000001</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.049159</v>
+        <v>-0.049159</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.16084</v>
+        <v>-0.16084</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.038257</v>
+        <v>-0.038257</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.044938</v>
+        <v>-0.044938</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.316992</v>
+        <v>-0.316992</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.717824</v>
+        <v>-1.717824</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.778854</v>
+        <v>-0.778854</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-1.675511</v>
@@ -1387,31 +1387,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.000943</v>
+        <v>-0.000943</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.06753000000000001</v>
+        <v>-0.06753000000000001</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.049159</v>
+        <v>-0.049159</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.16084</v>
+        <v>-0.16084</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.038257</v>
+        <v>-0.038257</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.044938</v>
+        <v>-0.044938</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.316992</v>
+        <v>-0.316992</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.717824</v>
+        <v>-1.717824</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.778854</v>
+        <v>-0.778854</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-1.675511</v>
@@ -1534,31 +1534,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.000943</v>
+        <v>-0.000943</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.06753000000000001</v>
+        <v>-0.06753000000000001</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.049159</v>
+        <v>-0.049159</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.16084</v>
+        <v>-0.16084</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.038257</v>
+        <v>-0.038257</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.044938</v>
+        <v>-0.044938</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.316992</v>
+        <v>-0.316992</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.717824</v>
+        <v>-1.717824</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.778854</v>
+        <v>-0.778854</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-1.675511</v>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-3.3765</v>
+        <v>3.3765</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-5.361333</v>
+        <v>5.361333</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-2.2469</v>
+        <v>2.2469</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-42.9456</v>
+        <v>42.9456</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-38.9427</v>
+        <v>38.9427</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>16.75511</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.000943</v>
+        <v>-0.000943</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.06753000000000001</v>
+        <v>-0.06753000000000001</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.049159</v>
+        <v>-0.049159</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.16084</v>
+        <v>-0.16084</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.038257</v>
+        <v>-0.038257</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.044938</v>
+        <v>-0.044938</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.316992</v>
+        <v>-0.316992</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.717824</v>
+        <v>-1.717824</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.778854</v>
+        <v>-0.778854</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-1.675511</v>
@@ -1836,31 +1836,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.000943</v>
+        <v>-0.000943</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.06753000000000001</v>
+        <v>-0.06753000000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.049159</v>
+        <v>-0.049159</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.16084</v>
+        <v>-0.16084</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.038257</v>
+        <v>-0.038257</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.044938</v>
+        <v>-0.044938</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.316992</v>
+        <v>-0.316992</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.717824</v>
+        <v>-1.717824</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.778854</v>
+        <v>-0.778854</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-1.675511</v>
@@ -1962,31 +1962,31 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -5036,16 +5036,16 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.575839</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.03474</v>
+        <v>0.773963</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.5757679999999999</v>
+        <v>3.231568</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>1.591395</v>
+        <v>4.221763</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>1.681232</v>
@@ -10558,7 +10558,11 @@
           <t>Warrant reserves 11</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -11512,7 +11516,11 @@
           <t>Warrant reserves 10</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -12464,7 +12472,11 @@
           <t>Warrant reserves 7</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -40797,10 +40809,10 @@
         </is>
       </c>
       <c r="L394" s="5" t="n">
-        <v>1.717824</v>
+        <v>-1.717824</v>
       </c>
       <c r="M394" s="5" t="n">
-        <v>0.778854</v>
+        <v>-0.778854</v>
       </c>
       <c r="N394" t="inlineStr">
         <is>
@@ -41730,10 +41742,10 @@
         </is>
       </c>
       <c r="K405" s="5" t="n">
-        <v>0.316992</v>
+        <v>-0.316992</v>
       </c>
       <c r="L405" s="5" t="n">
-        <v>1.717824</v>
+        <v>-1.717824</v>
       </c>
       <c r="M405" t="inlineStr">
         <is>
@@ -42089,22 +42101,22 @@
         </is>
       </c>
       <c r="F410" s="5" t="n">
-        <v>0.06753000000000001</v>
+        <v>-0.06753000000000001</v>
       </c>
       <c r="G410" s="5" t="n">
-        <v>0.049159</v>
+        <v>-0.049159</v>
       </c>
       <c r="H410" s="5" t="n">
-        <v>0.16084</v>
+        <v>-0.16084</v>
       </c>
       <c r="I410" s="5" t="n">
-        <v>0.038257</v>
+        <v>-0.038257</v>
       </c>
       <c r="J410" s="5" t="n">
-        <v>0.044938</v>
+        <v>-0.044938</v>
       </c>
       <c r="K410" s="5" t="n">
-        <v>0.052194</v>
+        <v>-0.052194</v>
       </c>
       <c r="L410" t="inlineStr">
         <is>
@@ -43015,7 +43027,7 @@
         </is>
       </c>
       <c r="J421" s="5" t="n">
-        <v>0.038257</v>
+        <v>-0.038257</v>
       </c>
       <c r="K421" t="inlineStr">
         <is>
@@ -46378,10 +46390,10 @@
         </is>
       </c>
       <c r="E461" s="5" t="n">
-        <v>0.000943</v>
+        <v>-0.000943</v>
       </c>
       <c r="F461" s="5" t="n">
-        <v>0.06753000000000001</v>
+        <v>-0.06753000000000001</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/STW.xlsx
+++ b/output/pdf_financials_xlsx/STW.xlsx
@@ -963,22 +963,22 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001543</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.00444</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.00503</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.003653</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.004578</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.004254</v>
       </c>
     </row>
     <row r="13">
@@ -1762,22 +1762,22 @@
         <v>-1.717824</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.778854</v>
+        <v>-0.777311</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.675511</v>
+        <v>-1.679951</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.498595</v>
+        <v>-1.503625</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.944359</v>
+        <v>-1.948012</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.588326</v>
+        <v>-0.592904</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-5.003061</v>
+        <v>-5.007315</v>
       </c>
     </row>
     <row r="28">
@@ -1860,22 +1860,22 @@
         <v>-1.717824</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.778854</v>
+        <v>-0.777311</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.675511</v>
+        <v>-1.679951</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.498595</v>
+        <v>-1.503625</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.944359</v>
+        <v>-1.948012</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.588326</v>
+        <v>-0.592904</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.003061</v>
+        <v>-5.007315</v>
       </c>
     </row>
     <row r="30">
@@ -2110,7 +2110,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.140392</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.492174</v>
@@ -2119,22 +2119,22 @@
         <v>0.425795</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.00221</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.642772</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.09622699999999999</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.200671</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.006164</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.06811300000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.140392</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.492174</v>
@@ -2217,22 +2217,22 @@
         <v>0.425795</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.00221</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.642772</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.09622699999999999</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.200671</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.006164</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.06811300000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2805,22 +2805,22 @@
         <v>0.176779</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.225369</v>
+        <v>0.223159</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.834824</v>
+        <v>0.192052</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.427631</v>
+        <v>0.331404</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.299562</v>
+        <v>0.09889100000000001</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.059735</v>
+        <v>0.053571</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.535483</v>
+        <v>0.46737</v>
       </c>
     </row>
     <row r="49">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -34702,7 +34702,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -35718,7 +35718,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -37338,7 +37338,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -37770,7 +37770,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -38292,7 +38292,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -38636,7 +38636,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -40596,7 +40596,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -41864,7 +41864,11 @@
           <t>General and administration expenses</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -42742,7 +42746,11 @@
           <t>General and administration expenses 436</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -45864,7 +45872,11 @@
           <t>General and administration expenses</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
           <t>-</t>
